--- a/assets/files/tesla-financial-model.xlsx
+++ b/assets/files/tesla-financial-model.xlsx
@@ -7,24 +7,28 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary &amp; Ratios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Valuation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary &amp; Ratios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Scenario Valuation'!$A$1:$F$28</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -210,8 +214,20 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -245,6 +261,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00393C41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -297,7 +323,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -703,6 +729,13 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -952,6 +985,352 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" style="67" min="1" max="1"/>
+    <col width="15" customWidth="1" style="67" min="2" max="2"/>
+    <col width="15" customWidth="1" style="67" min="3" max="3"/>
+    <col width="15" customWidth="1" style="67" min="4" max="4"/>
+    <col width="32" customWidth="1" style="67" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="137" t="inlineStr">
+        <is>
+          <t>Tesla (TSLA) — Scenario / Real-Options Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>USD bn / per share. 3,756M shares; net cash ~$36bn. Live $379 (Jul 2026). A conventional multiple is not meaningful (~375x earnings) — see Peer Comps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="138" t="inlineStr">
+        <is>
+          <t>CORE BUSINESS (SOTP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="139" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B6" s="139" t="inlineStr">
+        <is>
+          <t>Revenue ($bn)</t>
+        </is>
+      </c>
+      <c r="C6" s="139" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="D6" s="139" t="inlineStr">
+        <is>
+          <t>Value ($bn)</t>
+        </is>
+      </c>
+      <c r="E6" s="139" t="inlineStr"/>
+      <c r="F6" s="139" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="B7" s="66" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="C7" s="66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D7" s="140">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="66" t="inlineStr">
+        <is>
+          <t>Premium brand/tech @ 2.2x rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="66" t="inlineStr">
+        <is>
+          <t>Energy gen &amp; storage</t>
+        </is>
+      </c>
+      <c r="B8" s="66" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C8" s="66" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="140">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="66" t="inlineStr">
+        <is>
+          <t>+27% growth, margins rising @ 7x rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>Services &amp; Supercharging</t>
+        </is>
+      </c>
+      <c r="B9" s="66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C9" s="66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="140">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="66" t="inlineStr">
+        <is>
+          <t>Recurring @ 4x rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="66" t="inlineStr">
+        <is>
+          <t>Net cash</t>
+        </is>
+      </c>
+      <c r="B10" s="66" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="140">
+        <f>B10*C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="66" t="inlineStr">
+        <is>
+          <t>Balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="139" t="inlineStr">
+        <is>
+          <t>Core business value ($bn)</t>
+        </is>
+      </c>
+      <c r="D11" s="140">
+        <f>SUM(D7:D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="66" t="inlineStr">
+        <is>
+          <t>Core value per share ($)</t>
+        </is>
+      </c>
+      <c r="D12" s="141">
+        <f>D11*1000/3756</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="138" t="inlineStr">
+        <is>
+          <t>AUTONOMY + OPTIMUS OPTIONALITY (scenario-weighted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="139" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B16" s="139" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="C16" s="139" t="inlineStr">
+        <is>
+          <t>Optionality/share ($)</t>
+        </is>
+      </c>
+      <c r="D16" s="139" t="inlineStr">
+        <is>
+          <t>Value/share = core + option ($)</t>
+        </is>
+      </c>
+      <c r="E16" s="139" t="inlineStr"/>
+      <c r="F16" s="139" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="66" t="inlineStr">
+        <is>
+          <t>Bear — robotaxi/Optimus disappoint</t>
+        </is>
+      </c>
+      <c r="B17" s="142" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C17" s="141" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="141">
+        <f>$D$12+C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="66" t="inlineStr">
+        <is>
+          <t>Base — robotaxi scales to a real business</t>
+        </is>
+      </c>
+      <c r="B18" s="142" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C18" s="141" t="n">
+        <v>300</v>
+      </c>
+      <c r="D18" s="141">
+        <f>$D$12+C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="66" t="inlineStr">
+        <is>
+          <t>Bull — robotaxi + Optimus inflect</t>
+        </is>
+      </c>
+      <c r="B19" s="142" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C19" s="141" t="n">
+        <v>700</v>
+      </c>
+      <c r="D19" s="141">
+        <f>$D$12+C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="138" t="inlineStr">
+        <is>
+          <t>PROBABILITY-WEIGHTED VALUE &amp; RATING</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
+          <t>Probability-weighted value / share ($)</t>
+        </is>
+      </c>
+      <c r="B22" s="141">
+        <f>SUMPRODUCT(B17:B19,D17:D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="inlineStr">
+        <is>
+          <t>Current price ($)</t>
+        </is>
+      </c>
+      <c r="B23" s="66" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="inlineStr">
+        <is>
+          <t>Upside / (downside)</t>
+        </is>
+      </c>
+      <c r="B24" s="143">
+        <f>B22/B23-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="66" t="inlineStr">
+        <is>
+          <t>Scenario range ($/share)</t>
+        </is>
+      </c>
+      <c r="B25" s="141">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="C25" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to </t>
+        </is>
+      </c>
+      <c r="D25" s="141">
+        <f>D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="66" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="B26" s="66">
+        <f>IF(B24&gt;0.15,"BUY",IF(B24&gt;0.05,"ACCUMULATE",IF(B24&gt;-0.10,"HOLD","REDUCE")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="66" t="inlineStr">
+        <is>
+          <t>Note: Tesla cannot be valued on the FY25 P&amp;L (EPS $1.08). ~$290/share of the price is a real option on autonomy (robotaxi now live, no safety driver, 5+ cities) and Optimus. The outcomes are real, unproven and near-binary — the ~$117 (bear) to ~$787 (bull) range dwarfs the point estimate. Size to conviction on the story, not to a spreadsheet. HOLD.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF171A20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2008,7 +2387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF171A20"/>
@@ -3109,7 +3488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF171A20"/>
@@ -4225,7 +4604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF171A20"/>
@@ -5349,7 +5728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00393C41"/>
